--- a/docs/estimation/work-estimation.xlsx
+++ b/docs/estimation/work-estimation.xlsx
@@ -14,7 +14,7 @@
     <sheet name="How to use" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Work Breakdown'!$A$1:$S$115</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Work Breakdown'!$A$1:$S$122</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="719">
   <si>
     <t xml:space="preserve">Tuition Ledger — work estimate</t>
   </si>
@@ -407,6 +407,9 @@
     <t xml:space="preserve">04 §0</t>
   </si>
   <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
     <t xml:space="preserve">`./mvnw test` passes ModularityTests</t>
   </si>
   <si>
@@ -437,6 +440,9 @@
     <t xml:space="preserve">11</t>
   </si>
   <si>
+    <t xml:space="preserve">In progress</t>
+  </si>
+  <si>
     <t xml:space="preserve">App boots from .env.example values</t>
   </si>
   <si>
@@ -704,6 +710,66 @@
     <t xml:space="preserve">Invite → staff can log in; deactivate → logged out</t>
   </si>
   <si>
+    <t xml:space="preserve">Self-serve signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration API: POST /signup/otp + /signup (centre name, owner, email, WhatsApp number, password), OTP before any row, unique phone/email, 3 per phone/email/IP per day, 30-day trial; reuses NEW-04 provisioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-04, S1-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEN-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-0018, 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No centre row before OTP; duplicate phone/email refused; 4th signup per IP → 429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email + password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email + password sign-in: POST /auth/login, Argon2id, common-password list, 5-failure lock + WhatsApp notice, email verification, forgot/reset (email link or WhatsApp code), PATCH /me/credentials; transactional email provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEN-2, CEN-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-0019, 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock after 5 failures; used reset link refused; sessions revoked on reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signup + login UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE registration + OTP step, sign-in by WhatsApp code or email + password, forgot/reset screens, My account sign-in methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-10, NEW-11, S1-13d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEN-2, CEN-6, CEN-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">design/prototype.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both sign-in methods land on the same role; screens match the prototype</t>
+  </si>
+  <si>
     <t xml:space="preserve">Batches API</t>
   </si>
   <si>
@@ -914,6 +980,21 @@
     <t xml:space="preserve">Run twice → same count; kill at 60/118 and resume → 118</t>
   </si>
   <si>
+    <t xml:space="preserve">Fee run preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /fee-runs/{period}/preview: dry run with computation, writes nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEE-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preview equals the charges the run then creates</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adjustments</t>
   </si>
   <si>
@@ -953,9 +1034,6 @@
     <t xml:space="preserve">FE fee run page (preview, progress, resume) and one-off charge form</t>
   </si>
   <si>
-    <t xml:space="preserve">FEE-1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Progress 60/118 visible during run</t>
   </si>
   <si>
@@ -1010,6 +1088,18 @@
     <t xml:space="preserve">Originals unchanged; refund line referenced</t>
   </si>
   <si>
+    <t xml:space="preserve">Adjustments API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /adjustments: signed discount/credit/correction with required reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds a ledger line; nothing edited</t>
+  </si>
+  <si>
     <t xml:space="preserve">Statement</t>
   </si>
   <si>
@@ -1235,6 +1325,27 @@
     <t xml:space="preserve">Log shows template, variables, status</t>
   </si>
   <si>
+    <t xml:space="preserve">Sender status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre WhatsApp sender status (not_connected/pending/connected), embedded signup start, outbox `held` released on approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3-03, S3-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEN-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-0018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt recorded before approval is held, then sent on approval</t>
+  </si>
+  <si>
     <t xml:space="preserve">Consent UI</t>
   </si>
   <si>
@@ -1425,6 +1536,24 @@
   </si>
   <si>
     <t xml:space="preserve">10k rows stream without OOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List summaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students list filters hasBalance/consent + batchIds/attendanceRate30d; batch list summary fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1-09, S1-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-1, BAT-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One request per list screen; no N+1</t>
   </si>
   <si>
     <t xml:space="preserve">Low attendance</t>
@@ -2811,28 +2940,28 @@
         <v>10</v>
       </c>
       <c r="B6" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,A6)</f>
-        <v>150.5</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,A6)</f>
+        <v>159</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,A6)</f>
-        <v>182.925</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,A6)</f>
+        <v>193.5</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,A6)</f>
-        <v>731.7</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,A6)</f>
+        <v>774</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">C6/2</f>
-        <v>91.4625</v>
+        <v>96.75</v>
       </c>
       <c r="F6" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,A6,'Work Breakdown'!$R$2:$R$115,"Done")</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,A6,'Work Breakdown'!$R$2:$R$122,"Done")</f>
+        <v>2.2</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">IF(C6=0,0,F6/C6)</f>
-        <v>0</v>
+        <v>0.0113695090439277</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -2842,15 +2971,15 @@
         <v>11</v>
       </c>
       <c r="B7" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,A7)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,A7)</f>
         <v>96</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,A7)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,A7)</f>
         <v>115.2</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,A7)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,A7)</f>
         <v>460.8</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -2858,7 +2987,7 @@
         <v>57.6</v>
       </c>
       <c r="F7" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,A7,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,A7,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
@@ -2922,16 +3051,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A11)</f>
-        <v>101.5</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A11)</f>
+        <v>108</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A11)</f>
-        <v>124.85</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A11)</f>
+        <v>133.025</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A11)</f>
-        <v>499.4</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A11)</f>
+        <v>532.1</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">INDEX(Assumptions!$B$19:$B$22,MATCH(A11,Assumptions!$A$19:$A$22,0))</f>
@@ -2939,11 +3068,11 @@
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">IF(E11=0,0,C11/E11)</f>
-        <v>6.2425</v>
+        <v>6.65125</v>
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">F11*Assumptions!$B$4/5</f>
-        <v>12.485</v>
+        <v>13.3025</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -2953,16 +3082,16 @@
         <v>18</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A12)</f>
-        <v>34.5</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A12)</f>
+        <v>36.5</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A12)</f>
-        <v>40.1</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A12)</f>
+        <v>42.5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A12)</f>
-        <v>160.4</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A12)</f>
+        <v>170</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">INDEX(Assumptions!$B$19:$B$22,MATCH(A12,Assumptions!$A$19:$A$22,0))</f>
@@ -2970,11 +3099,11 @@
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">IF(E12=0,0,C12/E12)</f>
-        <v>5.0125</v>
+        <v>5.3125</v>
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">F12*Assumptions!$B$4/5</f>
-        <v>10.025</v>
+        <v>10.625</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -2984,15 +3113,15 @@
         <v>19</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A13)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A13)</f>
         <v>7.5</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A13)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A13)</f>
         <v>8.9</v>
       </c>
       <c r="D13" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A13)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A13)</f>
         <v>35.6</v>
       </c>
       <c r="E13" s="7" t="n">
@@ -3015,15 +3144,15 @@
         <v>20</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A14)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$L$2:$L$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A14)</f>
         <v>7</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A14)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A14)</f>
         <v>9.075</v>
       </c>
       <c r="D14" s="8" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$115,'Work Breakdown'!$B$2:$B$115,"MVP",'Work Breakdown'!$G$2:$G$115,A14)</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$P$2:$P$122,'Work Breakdown'!$B$2:$B$122,"MVP",'Work Breakdown'!$G$2:$G$122,A14)</f>
         <v>36.3</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -3051,11 +3180,11 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="n">
         <f aca="false">MAX(F11:F14)</f>
-        <v>6.2425</v>
+        <v>6.65125</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">MAX(G11:G14)</f>
-        <v>12.485</v>
+        <v>13.3025</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -3118,7 +3247,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A19,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A19,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>31.85</v>
       </c>
       <c r="C19" s="7" t="n">
@@ -3130,7 +3259,7 @@
         <v>1.5925</v>
       </c>
       <c r="E19" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A19,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A19,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>10.2</v>
       </c>
       <c r="F19" s="7" t="n">
@@ -3142,11 +3271,11 @@
         <v>1.275</v>
       </c>
       <c r="H19" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A19,'Work Breakdown'!$G$2:$G$115,"QA")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A19,'Work Breakdown'!$G$2:$G$122,"QA")</f>
         <v>1.1</v>
       </c>
       <c r="I19" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A19,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A19,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
     </row>
@@ -3155,8 +3284,8 @@
         <v>29</v>
       </c>
       <c r="B20" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A20,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>23.95</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A20,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>29.825</v>
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">Assumptions!$B$19</f>
@@ -3164,11 +3293,11 @@
       </c>
       <c r="D20" s="9" t="n">
         <f aca="false">IF(C20=0,0,B20/C20)</f>
-        <v>1.1975</v>
+        <v>1.49125</v>
       </c>
       <c r="E20" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A20,'Work Breakdown'!$G$2:$G$115,"FE")</f>
-        <v>10.45</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A20,'Work Breakdown'!$G$2:$G$122,"FE")</f>
+        <v>12.85</v>
       </c>
       <c r="F20" s="7" t="n">
         <f aca="false">Assumptions!$B$20</f>
@@ -3176,14 +3305,14 @@
       </c>
       <c r="G20" s="9" t="n">
         <f aca="false">IF(F20=0,0,E20/F20)</f>
-        <v>1.30625</v>
+        <v>1.60625</v>
       </c>
       <c r="H20" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A20,'Work Breakdown'!$G$2:$G$115,"QA")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A20,'Work Breakdown'!$G$2:$G$122,"QA")</f>
         <v>1.2</v>
       </c>
       <c r="I20" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A20,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A20,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
     </row>
@@ -3192,8 +3321,8 @@
         <v>30</v>
       </c>
       <c r="B21" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A21,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>23.7</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A21,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>24.9</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">Assumptions!$B$19</f>
@@ -3201,10 +3330,10 @@
       </c>
       <c r="D21" s="9" t="n">
         <f aca="false">IF(C21=0,0,B21/C21)</f>
-        <v>1.185</v>
+        <v>1.245</v>
       </c>
       <c r="E21" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A21,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A21,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>4.6</v>
       </c>
       <c r="F21" s="7" t="n">
@@ -3216,11 +3345,11 @@
         <v>0.575</v>
       </c>
       <c r="H21" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A21,'Work Breakdown'!$G$2:$G$115,"QA")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A21,'Work Breakdown'!$G$2:$G$122,"QA")</f>
         <v>1.8</v>
       </c>
       <c r="I21" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A21,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A21,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>1.35</v>
       </c>
     </row>
@@ -3229,8 +3358,8 @@
         <v>31</v>
       </c>
       <c r="B22" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A22,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>21.2</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A22,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>22.3</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">Assumptions!$B$19</f>
@@ -3238,10 +3367,10 @@
       </c>
       <c r="D22" s="9" t="n">
         <f aca="false">IF(C22=0,0,B22/C22)</f>
-        <v>1.06</v>
+        <v>1.115</v>
       </c>
       <c r="E22" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A22,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A22,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>7.7</v>
       </c>
       <c r="F22" s="7" t="n">
@@ -3253,11 +3382,11 @@
         <v>0.9625</v>
       </c>
       <c r="H22" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A22,'Work Breakdown'!$G$2:$G$115,"QA")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A22,'Work Breakdown'!$G$2:$G$122,"QA")</f>
         <v>2.4</v>
       </c>
       <c r="I22" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A22,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A22,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>3.3</v>
       </c>
     </row>
@@ -3266,7 +3395,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A23,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A23,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>24.15</v>
       </c>
       <c r="C23" s="7" t="n">
@@ -3278,7 +3407,7 @@
         <v>1.2075</v>
       </c>
       <c r="E23" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A23,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A23,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>7.15</v>
       </c>
       <c r="F23" s="7" t="n">
@@ -3290,11 +3419,11 @@
         <v>0.89375</v>
       </c>
       <c r="H23" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A23,'Work Breakdown'!$G$2:$G$115,"QA")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A23,'Work Breakdown'!$G$2:$G$122,"QA")</f>
         <v>2.4</v>
       </c>
       <c r="I23" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$I$2:$I$115,A23,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$I$2:$I$122,A23,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>4.425</v>
       </c>
     </row>
@@ -3367,15 +3496,15 @@
         <v>41</v>
       </c>
       <c r="B28" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A28,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A28,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>8.2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A28,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A28,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>2.75</v>
       </c>
       <c r="D28" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A28,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A28,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A28,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A28,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
@@ -3387,12 +3516,12 @@
         <v>43.8</v>
       </c>
       <c r="G28" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A28,'Work Breakdown'!$R$2:$R$115,"Done")</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A28,'Work Breakdown'!$R$2:$R$122,"Done")</f>
+        <v>2.2</v>
       </c>
       <c r="H28" s="9" t="n">
         <f aca="false">IF(E28=0,0,G28/E28)</f>
-        <v>0</v>
+        <v>0.200913242009132</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -3401,15 +3530,15 @@
         <v>42</v>
       </c>
       <c r="B29" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A29,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A29,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>6.6</v>
       </c>
       <c r="C29" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A29,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A29,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>0</v>
       </c>
       <c r="D29" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A29,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A29,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A29,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A29,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
@@ -3421,7 +3550,7 @@
         <v>26.4</v>
       </c>
       <c r="G29" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A29,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A29,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
@@ -3435,27 +3564,27 @@
         <v>43</v>
       </c>
       <c r="B30" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A30,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>7.55</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A30,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>12.275</v>
       </c>
       <c r="C30" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A30,'Work Breakdown'!$G$2:$G$115,"FE")</f>
-        <v>3.4</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A30,'Work Breakdown'!$G$2:$G$122,"FE")</f>
+        <v>5.8</v>
       </c>
       <c r="D30" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A30,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A30,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A30,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A30,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">SUM(B30:D30)</f>
-        <v>10.95</v>
+        <v>18.075</v>
       </c>
       <c r="F30" s="8" t="n">
         <f aca="false">E30*Assumptions!$B$3</f>
-        <v>43.8</v>
+        <v>72.3</v>
       </c>
       <c r="G30" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A30,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A30,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
@@ -3469,15 +3598,15 @@
         <v>44</v>
       </c>
       <c r="B31" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A31,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A31,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>3.6</v>
       </c>
       <c r="C31" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A31,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A31,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>3.3</v>
       </c>
       <c r="D31" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A31,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A31,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A31,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A31,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
@@ -3489,7 +3618,7 @@
         <v>27.6</v>
       </c>
       <c r="G31" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A31,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A31,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
@@ -3503,15 +3632,15 @@
         <v>45</v>
       </c>
       <c r="B32" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A32,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A32,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>2.4</v>
       </c>
       <c r="C32" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A32,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A32,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>2.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A32,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A32,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A32,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A32,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
@@ -3523,7 +3652,7 @@
         <v>18.4</v>
       </c>
       <c r="G32" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A32,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A32,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
@@ -3537,15 +3666,15 @@
         <v>46</v>
       </c>
       <c r="B33" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A33,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A33,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>3.5</v>
       </c>
       <c r="C33" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A33,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A33,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>2.4</v>
       </c>
       <c r="D33" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A33,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A33,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A33,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A33,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>1.1</v>
       </c>
       <c r="E33" s="7" t="n">
@@ -3557,7 +3686,7 @@
         <v>28</v>
       </c>
       <c r="G33" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A33,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A33,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
@@ -3571,27 +3700,27 @@
         <v>47</v>
       </c>
       <c r="B34" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A34,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>11.2</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A34,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>11.8</v>
       </c>
       <c r="C34" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A34,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A34,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>1.8</v>
       </c>
       <c r="D34" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A34,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A34,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A34,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A34,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(B34:D34)</f>
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="F34" s="8" t="n">
         <f aca="false">E34*Assumptions!$B$3</f>
-        <v>52</v>
+        <v>54.4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A34,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A34,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
@@ -3605,27 +3734,27 @@
         <v>48</v>
       </c>
       <c r="B35" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A35,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>12.75</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A35,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>13.3</v>
       </c>
       <c r="C35" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A35,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A35,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>4.8</v>
       </c>
       <c r="D35" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A35,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A35,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A35,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A35,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>1.2</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(B35:D35)</f>
-        <v>18.75</v>
+        <v>19.3</v>
       </c>
       <c r="F35" s="8" t="n">
         <f aca="false">E35*Assumptions!$B$3</f>
-        <v>75</v>
+        <v>77.2</v>
       </c>
       <c r="G35" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A35,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A35,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
@@ -3639,27 +3768,27 @@
         <v>49</v>
       </c>
       <c r="B36" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A36,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>17.45</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A36,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>18.65</v>
       </c>
       <c r="C36" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A36,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A36,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>1.65</v>
       </c>
       <c r="D36" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A36,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A36,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A36,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A36,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0.675</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">SUM(B36:D36)</f>
-        <v>19.775</v>
+        <v>20.975</v>
       </c>
       <c r="F36" s="8" t="n">
         <f aca="false">E36*Assumptions!$B$3</f>
-        <v>79.1</v>
+        <v>83.9</v>
       </c>
       <c r="G36" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A36,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A36,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
@@ -3673,15 +3802,15 @@
         <v>50</v>
       </c>
       <c r="B37" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A37,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A37,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>6.25</v>
       </c>
       <c r="C37" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A37,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A37,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>2.95</v>
       </c>
       <c r="D37" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A37,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A37,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A37,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A37,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>2.475</v>
       </c>
       <c r="E37" s="7" t="n">
@@ -3693,7 +3822,7 @@
         <v>46.7</v>
       </c>
       <c r="G37" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A37,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A37,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
@@ -3707,15 +3836,15 @@
         <v>51</v>
       </c>
       <c r="B38" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A38,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A38,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>6.4</v>
       </c>
       <c r="C38" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A38,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A38,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A38,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A38,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A38,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A38,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
@@ -3727,7 +3856,7 @@
         <v>25.6</v>
       </c>
       <c r="G38" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A38,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A38,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
@@ -3741,27 +3870,27 @@
         <v>52</v>
       </c>
       <c r="B39" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A39,'Work Breakdown'!$G$2:$G$115,"BE")</f>
-        <v>7.6</v>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A39,'Work Breakdown'!$G$2:$G$122,"BE")</f>
+        <v>8.7</v>
       </c>
       <c r="C39" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A39,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A39,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>6.6</v>
       </c>
       <c r="D39" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A39,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A39,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A39,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A39,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">SUM(B39:D39)</f>
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="F39" s="8" t="n">
         <f aca="false">E39*Assumptions!$B$3</f>
-        <v>56.8</v>
+        <v>61.2</v>
       </c>
       <c r="G39" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A39,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A39,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
@@ -3775,15 +3904,15 @@
         <v>53</v>
       </c>
       <c r="B40" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A40,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A40,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>4.2</v>
       </c>
       <c r="C40" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A40,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A40,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>1.1</v>
       </c>
       <c r="D40" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A40,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A40,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A40,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A40,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E40" s="7" t="n">
@@ -3795,7 +3924,7 @@
         <v>21.2</v>
       </c>
       <c r="G40" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A40,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A40,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
@@ -3809,15 +3938,15 @@
         <v>54</v>
       </c>
       <c r="B41" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A41,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A41,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>3</v>
       </c>
       <c r="C41" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A41,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A41,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>0</v>
       </c>
       <c r="D41" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A41,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A41,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A41,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A41,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>5.7</v>
       </c>
       <c r="E41" s="7" t="n">
@@ -3829,7 +3958,7 @@
         <v>34.8</v>
       </c>
       <c r="G41" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A41,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A41,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
@@ -3843,15 +3972,15 @@
         <v>55</v>
       </c>
       <c r="B42" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A42,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A42,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>4.8</v>
       </c>
       <c r="C42" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A42,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A42,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>3</v>
       </c>
       <c r="D42" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A42,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A42,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A42,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A42,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0.675</v>
       </c>
       <c r="E42" s="7" t="n">
@@ -3863,7 +3992,7 @@
         <v>33.9</v>
       </c>
       <c r="G42" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A42,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A42,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
@@ -3877,15 +4006,15 @@
         <v>56</v>
       </c>
       <c r="B43" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A43,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A43,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>8.55</v>
       </c>
       <c r="C43" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A43,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A43,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>3.6</v>
       </c>
       <c r="D43" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A43,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A43,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A43,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A43,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
@@ -3897,7 +4026,7 @@
         <v>48.6</v>
       </c>
       <c r="G43" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A43,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A43,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
@@ -3911,15 +4040,15 @@
         <v>57</v>
       </c>
       <c r="B44" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A44,'Work Breakdown'!$G$2:$G$115,"BE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A44,'Work Breakdown'!$G$2:$G$122,"BE")</f>
         <v>10.8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A44,'Work Breakdown'!$G$2:$G$115,"FE")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A44,'Work Breakdown'!$G$2:$G$122,"FE")</f>
         <v>0.55</v>
       </c>
       <c r="D44" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A44,'Work Breakdown'!$G$2:$G$115,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A44,'Work Breakdown'!$G$2:$G$115,"PM")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A44,'Work Breakdown'!$G$2:$G$122,"QA")+SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A44,'Work Breakdown'!$G$2:$G$122,"PM")</f>
         <v>6.15</v>
       </c>
       <c r="E44" s="7" t="n">
@@ -3931,7 +4060,7 @@
         <v>70</v>
       </c>
       <c r="G44" s="7" t="n">
-        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$115,'Work Breakdown'!$C$2:$C$115,A44,'Work Breakdown'!$R$2:$R$115,"Done")</f>
+        <f aca="false">SUMIFS('Work Breakdown'!$O$2:$O$122,'Work Breakdown'!$C$2:$C$122,A44,'Work Breakdown'!$R$2:$R$122,"Done")</f>
         <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
@@ -3946,11 +4075,11 @@
       </c>
       <c r="B45" s="12" t="n">
         <f aca="false">SUM(B28:B44)</f>
-        <v>124.85</v>
+        <v>133.025</v>
       </c>
       <c r="C45" s="12" t="n">
         <f aca="false">SUM(C28:C44)</f>
-        <v>40.1</v>
+        <v>42.5</v>
       </c>
       <c r="D45" s="12" t="n">
         <f aca="false">SUM(D28:D44)</f>
@@ -3958,19 +4087,19 @@
       </c>
       <c r="E45" s="12" t="n">
         <f aca="false">SUM(E28:E44)</f>
-        <v>182.925</v>
+        <v>193.5</v>
       </c>
       <c r="F45" s="13" t="n">
         <f aca="false">SUM(F28:F44)</f>
-        <v>731.7</v>
+        <v>774</v>
       </c>
       <c r="G45" s="12" t="n">
         <f aca="false">SUM(G28:G44)</f>
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H45" s="9" t="n">
         <f aca="false">IF(E45=0,0,G45/E45)</f>
-        <v>0</v>
+        <v>0.0113695090439277</v>
       </c>
       <c r="I45" s="4"/>
     </row>
@@ -4260,7 +4389,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4454,10 +4583,10 @@
       </c>
       <c r="Q3" s="26"/>
       <c r="R3" s="26" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="S3" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4471,13 +4600,13 @@
         <v>41</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>18</v>
@@ -4492,7 +4621,7 @@
         <v>104</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L4" s="22" t="n">
         <v>1</v>
@@ -4514,10 +4643,10 @@
       </c>
       <c r="Q4" s="26"/>
       <c r="R4" s="26" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4531,13 +4660,13 @@
         <v>41</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>17</v>
@@ -4552,7 +4681,7 @@
         <v>104</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L5" s="22" t="n">
         <v>0.5</v>
@@ -4574,10 +4703,10 @@
       </c>
       <c r="Q5" s="26"/>
       <c r="R5" s="26" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="S5" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4591,13 +4720,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>17</v>
@@ -4637,7 +4766,7 @@
         <v>106</v>
       </c>
       <c r="S6" s="20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4651,19 +4780,19 @@
         <v>41</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I7" s="20" t="s">
         <v>28</v>
@@ -4672,7 +4801,7 @@
         <v>104</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L7" s="22" t="n">
         <v>1</v>
@@ -4697,7 +4826,7 @@
         <v>106</v>
       </c>
       <c r="S7" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4711,13 +4840,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>17</v>
@@ -4729,10 +4858,10 @@
         <v>28</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L8" s="22" t="n">
         <v>2</v>
@@ -4757,7 +4886,7 @@
         <v>106</v>
       </c>
       <c r="S8" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4771,19 +4900,19 @@
         <v>41</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I9" s="20" t="s">
         <v>28</v>
@@ -4792,7 +4921,7 @@
         <v>104</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L9" s="22" t="n">
         <v>0.5</v>
@@ -4817,7 +4946,7 @@
         <v>106</v>
       </c>
       <c r="S9" s="20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4831,28 +4960,28 @@
         <v>41</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K10" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L10" s="22" t="n">
         <v>1</v>
@@ -4877,7 +5006,7 @@
         <v>106</v>
       </c>
       <c r="S10" s="20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4891,28 +5020,28 @@
         <v>41</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I11" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L11" s="22" t="n">
         <v>1</v>
@@ -4937,7 +5066,7 @@
         <v>106</v>
       </c>
       <c r="S11" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4951,13 +5080,13 @@
         <v>42</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>17</v>
@@ -4972,7 +5101,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" s="22" t="n">
         <v>2</v>
@@ -4997,7 +5126,7 @@
         <v>106</v>
       </c>
       <c r="S12" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5011,28 +5140,28 @@
         <v>42</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I13" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L13" s="22" t="n">
         <v>1</v>
@@ -5057,7 +5186,7 @@
         <v>106</v>
       </c>
       <c r="S13" s="20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5071,28 +5200,28 @@
         <v>42</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I14" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L14" s="22" t="n">
         <v>2</v>
@@ -5117,7 +5246,7 @@
         <v>106</v>
       </c>
       <c r="S14" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5131,28 +5260,28 @@
         <v>43</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I15" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L15" s="22" t="n">
         <v>3</v>
@@ -5177,7 +5306,7 @@
         <v>106</v>
       </c>
       <c r="S15" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5191,28 +5320,28 @@
         <v>43</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I16" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L16" s="22" t="n">
         <v>2</v>
@@ -5237,7 +5366,7 @@
         <v>106</v>
       </c>
       <c r="S16" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5251,28 +5380,28 @@
         <v>43</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I17" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L17" s="22" t="n">
         <v>1</v>
@@ -5297,7 +5426,7 @@
         <v>106</v>
       </c>
       <c r="S17" s="20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5311,28 +5440,28 @@
         <v>43</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L18" s="22" t="n">
         <v>1</v>
@@ -5357,7 +5486,7 @@
         <v>106</v>
       </c>
       <c r="S18" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5371,28 +5500,28 @@
         <v>43</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I19" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L19" s="22" t="n">
         <v>0.5</v>
@@ -5417,7 +5546,7 @@
         <v>106</v>
       </c>
       <c r="S19" s="20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5431,28 +5560,28 @@
         <v>43</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L20" s="22" t="n">
         <v>1.5</v>
@@ -5477,7 +5606,7 @@
         <v>106</v>
       </c>
       <c r="S20" s="20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5487,57 +5616,57 @@
       <c r="B21" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>44</v>
+      <c r="C21" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L21" s="22" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M21" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M21,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">L21*(1+N21)</f>
-        <v>3.6</v>
+        <v>2.025</v>
       </c>
       <c r="P21" s="25" t="n">
         <f aca="false">O21*Assumptions!$B$3</f>
-        <v>14.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q21" s="26"/>
       <c r="R21" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S21" s="20" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5548,56 +5677,56 @@
         <v>10</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="L22" s="22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M22" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N22" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M22,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">L22*(1+N22)</f>
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="P22" s="25" t="n">
         <f aca="false">O22*Assumptions!$B$3</f>
-        <v>6.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q22" s="26"/>
       <c r="R22" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S22" s="20" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5608,56 +5737,56 @@
         <v>10</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="I23" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M23" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N23" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M23,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O23" s="24" t="n">
         <f aca="false">L23*(1+N23)</f>
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="P23" s="25" t="n">
         <f aca="false">O23*Assumptions!$B$3</f>
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q23" s="26"/>
       <c r="R23" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S23" s="20" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5668,34 +5797,34 @@
         <v>10</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I24" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L24" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" s="22" t="s">
         <v>86</v>
@@ -5706,18 +5835,18 @@
       </c>
       <c r="O24" s="24" t="n">
         <f aca="false">L24*(1+N24)</f>
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="P24" s="25" t="n">
         <f aca="false">O24*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="Q24" s="26"/>
       <c r="R24" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S24" s="20" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5728,31 +5857,31 @@
         <v>10</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I25" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L25" s="22" t="n">
         <v>1.5</v>
@@ -5777,7 +5906,7 @@
         <v>106</v>
       </c>
       <c r="S25" s="20" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5788,34 +5917,34 @@
         <v>10</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="I26" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L26" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M26" s="22" t="s">
         <v>84</v>
@@ -5826,18 +5955,18 @@
       </c>
       <c r="O26" s="24" t="n">
         <f aca="false">L26*(1+N26)</f>
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="P26" s="25" t="n">
         <f aca="false">O26*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="Q26" s="26"/>
       <c r="R26" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S26" s="20" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5848,31 +5977,31 @@
         <v>10</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="I27" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="L27" s="22" t="n">
         <v>2</v>
@@ -5897,7 +6026,7 @@
         <v>106</v>
       </c>
       <c r="S27" s="20" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5908,56 +6037,56 @@
         <v>10</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I28" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L28" s="22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M28" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N28" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M28,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O28" s="24" t="n">
         <f aca="false">L28*(1+N28)</f>
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="P28" s="25" t="n">
         <f aca="false">O28*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q28" s="26"/>
       <c r="R28" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S28" s="20" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5968,34 +6097,34 @@
         <v>10</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="E29" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>246</v>
-      </c>
       <c r="I29" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="L29" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M29" s="22" t="s">
         <v>84</v>
@@ -6006,18 +6135,18 @@
       </c>
       <c r="O29" s="24" t="n">
         <f aca="false">L29*(1+N29)</f>
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="P29" s="25" t="n">
         <f aca="false">O29*Assumptions!$B$3</f>
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" s="26"/>
       <c r="R29" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S29" s="20" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6027,57 +6156,57 @@
       <c r="B30" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>19</v>
+        <v>267</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I30" s="20" t="s">
         <v>28</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="K30" s="20" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="L30" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N30" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M30,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O30" s="24" t="n">
         <f aca="false">L30*(1+N30)</f>
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="P30" s="25" t="n">
         <f aca="false">O30*Assumptions!$B$3</f>
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="Q30" s="26"/>
       <c r="R30" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S30" s="20" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6087,35 +6216,35 @@
       <c r="B31" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>47</v>
+      <c r="C31" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="I31" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>104</v>
+        <v>277</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" s="22" t="s">
         <v>86</v>
@@ -6126,18 +6255,18 @@
       </c>
       <c r="O31" s="24" t="n">
         <f aca="false">L31*(1+N31)</f>
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="P31" s="25" t="n">
         <f aca="false">O31*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q31" s="26"/>
       <c r="R31" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S31" s="20" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6148,56 +6277,56 @@
         <v>10</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G32" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="K32" s="20" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N32" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M32,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="O32" s="24" t="n">
         <f aca="false">L32*(1+N32)</f>
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="P32" s="25" t="n">
         <f aca="false">O32*Assumptions!$B$3</f>
-        <v>10.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q32" s="26"/>
       <c r="R32" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6208,56 +6337,56 @@
         <v>10</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>278</v>
+        <v>104</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M33" s="22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N33" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M33,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="O33" s="24" t="n">
         <f aca="false">L33*(1+N33)</f>
-        <v>4.05</v>
+        <v>1.1</v>
       </c>
       <c r="P33" s="25" t="n">
         <f aca="false">O33*Assumptions!$B$3</f>
-        <v>16.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q33" s="26"/>
       <c r="R33" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S33" s="20" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6267,57 +6396,57 @@
       <c r="B34" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>281</v>
+        <v>159</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="I34" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="K34" s="20" t="s">
-        <v>273</v>
+        <v>162</v>
       </c>
       <c r="L34" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M34,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O34" s="24" t="n">
         <f aca="false">L34*(1+N34)</f>
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="25" t="n">
         <f aca="false">O34*Assumptions!$B$3</f>
-        <v>10.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q34" s="26"/>
       <c r="R34" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S34" s="20" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6331,53 +6460,53 @@
         <v>47</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G35" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>266</v>
+        <v>136</v>
       </c>
       <c r="I35" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="L35" s="22" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N35" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M35,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O35" s="24" t="n">
         <f aca="false">L35*(1+N35)</f>
-        <v>0.55</v>
+        <v>2.7</v>
       </c>
       <c r="P35" s="25" t="n">
         <f aca="false">O35*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q35" s="26"/>
       <c r="R35" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S35" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6391,53 +6520,53 @@
         <v>47</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E36" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="20" t="s">
         <v>292</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>276</v>
       </c>
       <c r="I36" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K36" s="20" t="s">
-        <v>198</v>
+        <v>301</v>
       </c>
       <c r="L36" s="22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M36" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N36" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M36,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O36" s="24" t="n">
         <f aca="false">L36*(1+N36)</f>
-        <v>1.8</v>
+        <v>4.05</v>
       </c>
       <c r="P36" s="25" t="n">
         <f aca="false">O36*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>16.2</v>
       </c>
       <c r="Q36" s="26"/>
       <c r="R36" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S36" s="20" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6447,57 +6576,57 @@
       <c r="B37" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>48</v>
+      <c r="C37" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="I37" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L37" s="22" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M37" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N37" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M37,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O37" s="24" t="n">
         <f aca="false">L37*(1+N37)</f>
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="P37" s="25" t="n">
         <f aca="false">O37*Assumptions!$B$3</f>
-        <v>10.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" s="26"/>
       <c r="R37" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S37" s="20" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6508,34 +6637,34 @@
         <v>10</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G38" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I38" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J38" s="20" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="K38" s="20" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="L38" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M38" s="22" t="s">
         <v>88</v>
@@ -6546,18 +6675,18 @@
       </c>
       <c r="O38" s="24" t="n">
         <f aca="false">L38*(1+N38)</f>
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="P38" s="25" t="n">
         <f aca="false">O38*Assumptions!$B$3</f>
-        <v>16.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q38" s="26"/>
       <c r="R38" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S38" s="20" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6568,56 +6697,56 @@
         <v>10</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G39" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I39" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L39" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M39" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N39" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M39,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O39" s="24" t="n">
         <f aca="false">L39*(1+N39)</f>
-        <v>1.2</v>
+        <v>0.55</v>
       </c>
       <c r="P39" s="25" t="n">
         <f aca="false">O39*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" s="26"/>
       <c r="R39" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S39" s="20" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6628,34 +6757,34 @@
         <v>10</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I40" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>317</v>
+        <v>200</v>
       </c>
       <c r="L40" s="22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M40" s="22" t="s">
         <v>86</v>
@@ -6666,18 +6795,18 @@
       </c>
       <c r="O40" s="24" t="n">
         <f aca="false">L40*(1+N40)</f>
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="P40" s="25" t="n">
         <f aca="false">O40*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q40" s="26"/>
       <c r="R40" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S40" s="20" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6687,57 +6816,57 @@
       <c r="B41" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="21" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G41" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I41" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L41" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N41" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M41,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O41" s="24" t="n">
         <f aca="false">L41*(1+N41)</f>
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="P41" s="25" t="n">
         <f aca="false">O41*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q41" s="26"/>
       <c r="R41" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S41" s="20" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6751,53 +6880,53 @@
         <v>48</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="I42" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>198</v>
+        <v>332</v>
       </c>
       <c r="L42" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N42" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M42,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O42" s="24" t="n">
         <f aca="false">L42*(1+N42)</f>
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="P42" s="25" t="n">
         <f aca="false">O42*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>16.2</v>
       </c>
       <c r="Q42" s="26"/>
       <c r="R42" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S42" s="20" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6811,31 +6940,31 @@
         <v>48</v>
       </c>
       <c r="D43" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="20" t="s">
         <v>329</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>303</v>
       </c>
       <c r="I43" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>198</v>
+        <v>326</v>
       </c>
       <c r="L43" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="22" t="s">
         <v>86</v>
@@ -6846,18 +6975,18 @@
       </c>
       <c r="O43" s="24" t="n">
         <f aca="false">L43*(1+N43)</f>
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="P43" s="25" t="n">
         <f aca="false">O43*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q43" s="26"/>
       <c r="R43" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S43" s="20" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6871,53 +7000,53 @@
         <v>48</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>19</v>
+        <v>339</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I44" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>104</v>
+        <v>337</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="L44" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M44" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N44" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M44,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O44" s="24" t="n">
         <f aca="false">L44*(1+N44)</f>
-        <v>1.2</v>
+        <v>0.55</v>
       </c>
       <c r="P44" s="25" t="n">
         <f aca="false">O44*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" s="26"/>
       <c r="R44" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S44" s="20" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6931,31 +7060,31 @@
         <v>48</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G45" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I45" s="20" t="s">
         <v>29</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="L45" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" s="22" t="s">
         <v>86</v>
@@ -6966,18 +7095,18 @@
       </c>
       <c r="O45" s="24" t="n">
         <f aca="false">L45*(1+N45)</f>
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="P45" s="25" t="n">
         <f aca="false">O45*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q45" s="26"/>
       <c r="R45" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S45" s="20" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6987,57 +7116,57 @@
       <c r="B46" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="21" t="s">
-        <v>49</v>
+      <c r="C46" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>157</v>
+        <v>349</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G46" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J46" s="20" t="s">
         <v>104</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M46" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N46" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M46,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O46" s="24" t="n">
         <f aca="false">L46*(1+N46)</f>
-        <v>0.55</v>
+        <v>1.2</v>
       </c>
       <c r="P46" s="25" t="n">
         <f aca="false">O46*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q46" s="26"/>
       <c r="R46" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S46" s="20" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7048,31 +7177,31 @@
         <v>10</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>349</v>
+        <v>200</v>
       </c>
       <c r="L47" s="22" t="n">
         <v>2</v>
@@ -7097,7 +7226,7 @@
         <v>106</v>
       </c>
       <c r="S47" s="20" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7108,56 +7237,56 @@
         <v>10</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J48" s="20" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="K48" s="20" t="s">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="L48" s="22" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M48" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N48" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M48,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O48" s="24" t="n">
         <f aca="false">L48*(1+N48)</f>
-        <v>0.675</v>
+        <v>2.4</v>
       </c>
       <c r="P48" s="25" t="n">
         <f aca="false">O48*Assumptions!$B$3</f>
-        <v>2.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q48" s="26"/>
       <c r="R48" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S48" s="20" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7168,56 +7297,56 @@
         <v>10</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>357</v>
+        <v>19</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="K49" s="20" t="s">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="L49" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M49" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N49" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M49,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O49" s="24" t="n">
         <f aca="false">L49*(1+N49)</f>
-        <v>4.05</v>
+        <v>1.2</v>
       </c>
       <c r="P49" s="25" t="n">
         <f aca="false">O49*Assumptions!$B$3</f>
-        <v>16.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q49" s="26"/>
       <c r="R49" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S49" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7228,56 +7357,56 @@
         <v>10</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G50" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I50" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J50" s="20" t="s">
-        <v>366</v>
+        <v>104</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L50" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N50" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M50,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O50" s="24" t="n">
         <f aca="false">L50*(1+N50)</f>
-        <v>4.05</v>
+        <v>1.2</v>
       </c>
       <c r="P50" s="25" t="n">
         <f aca="false">O50*Assumptions!$B$3</f>
-        <v>16.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q50" s="26"/>
       <c r="R50" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S50" s="20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7287,57 +7416,57 @@
       <c r="B51" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>369</v>
+        <v>159</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G51" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="I51" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>372</v>
+        <v>104</v>
       </c>
       <c r="K51" s="20" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="L51" s="22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M51" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N51" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M51,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O51" s="24" t="n">
         <f aca="false">L51*(1+N51)</f>
-        <v>1.8</v>
+        <v>0.55</v>
       </c>
       <c r="P51" s="25" t="n">
         <f aca="false">O51*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" s="26"/>
       <c r="R51" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S51" s="20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7351,28 +7480,28 @@
         <v>49</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G52" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="I52" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J52" s="20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K52" s="20" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="L52" s="22" t="n">
         <v>2</v>
@@ -7397,7 +7526,7 @@
         <v>106</v>
       </c>
       <c r="S52" s="20" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7411,53 +7540,53 @@
         <v>49</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="I53" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="L53" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M53" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N53" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M53,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O53" s="24" t="n">
         <f aca="false">L53*(1+N53)</f>
-        <v>1.1</v>
+        <v>0.675</v>
       </c>
       <c r="P53" s="25" t="n">
         <f aca="false">O53*Assumptions!$B$3</f>
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q53" s="26"/>
       <c r="R53" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S53" s="20" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7471,53 +7600,53 @@
         <v>49</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G54" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I54" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J54" s="20" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K54" s="20" t="s">
-        <v>198</v>
+        <v>391</v>
       </c>
       <c r="L54" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M54" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N54" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M54,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O54" s="24" t="n">
         <f aca="false">L54*(1+N54)</f>
-        <v>1.1</v>
+        <v>4.05</v>
       </c>
       <c r="P54" s="25" t="n">
         <f aca="false">O54*Assumptions!$B$3</f>
-        <v>4.4</v>
+        <v>16.2</v>
       </c>
       <c r="Q54" s="26"/>
       <c r="R54" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S54" s="20" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7531,53 +7660,53 @@
         <v>49</v>
       </c>
       <c r="D55" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="20" t="s">
         <v>388</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>370</v>
       </c>
       <c r="I55" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J55" s="20" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="K55" s="20" t="s">
-        <v>198</v>
+        <v>397</v>
       </c>
       <c r="L55" s="22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M55" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N55" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M55,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O55" s="24" t="n">
         <f aca="false">L55*(1+N55)</f>
-        <v>1.65</v>
+        <v>4.05</v>
       </c>
       <c r="P55" s="25" t="n">
         <f aca="false">O55*Assumptions!$B$3</f>
-        <v>6.6</v>
+        <v>16.2</v>
       </c>
       <c r="Q55" s="26"/>
       <c r="R55" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S55" s="20" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7587,57 +7716,57 @@
       <c r="B56" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C56" s="21" t="s">
-        <v>50</v>
+      <c r="C56" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E56" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="20" t="s">
         <v>394</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>104</v>
       </c>
       <c r="I56" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J56" s="20" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K56" s="20" t="s">
-        <v>397</v>
+        <v>254</v>
       </c>
       <c r="L56" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M56" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N56" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M56,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O56" s="24" t="n">
         <f aca="false">L56*(1+N56)</f>
-        <v>0.675</v>
+        <v>1.8</v>
       </c>
       <c r="P56" s="25" t="n">
         <f aca="false">O56*Assumptions!$B$3</f>
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q56" s="26"/>
       <c r="R56" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S56" s="20" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7648,56 +7777,56 @@
         <v>10</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="G57" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>303</v>
+        <v>394</v>
       </c>
       <c r="I57" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="K57" s="20" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="L57" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N57" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M57,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O57" s="24" t="n">
         <f aca="false">L57*(1+N57)</f>
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="P57" s="25" t="n">
         <f aca="false">O57*Assumptions!$B$3</f>
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q57" s="26"/>
       <c r="R57" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S57" s="20" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7708,31 +7837,31 @@
         <v>10</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="G58" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="I58" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J58" s="20" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>198</v>
+        <v>391</v>
       </c>
       <c r="L58" s="22" t="n">
         <v>1</v>
@@ -7757,7 +7886,7 @@
         <v>106</v>
       </c>
       <c r="S58" s="20" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7768,56 +7897,56 @@
         <v>10</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="I59" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J59" s="20" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K59" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L59" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N59" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M59,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O59" s="24" t="n">
         <f aca="false">L59*(1+N59)</f>
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="P59" s="25" t="n">
         <f aca="false">O59*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q59" s="26"/>
       <c r="R59" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S59" s="20" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7828,56 +7957,56 @@
         <v>10</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G60" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="I60" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J60" s="20" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K60" s="20" t="s">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="L60" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M60" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N60" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M60,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O60" s="24" t="n">
         <f aca="false">L60*(1+N60)</f>
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="P60" s="25" t="n">
         <f aca="false">O60*Assumptions!$B$3</f>
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q60" s="26"/>
       <c r="R60" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S60" s="20" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7888,34 +8017,34 @@
         <v>10</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="I61" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="K61" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L61" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M61" s="22" t="s">
         <v>84</v>
@@ -7926,18 +8055,18 @@
       </c>
       <c r="O61" s="24" t="n">
         <f aca="false">L61*(1+N61)</f>
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="P61" s="25" t="n">
         <f aca="false">O61*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="Q61" s="26"/>
       <c r="R61" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S61" s="20" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7947,57 +8076,57 @@
       <c r="B62" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="21" t="s">
         <v>50</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>19</v>
+        <v>430</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>400</v>
+        <v>104</v>
       </c>
       <c r="I62" s="20" t="s">
         <v>30</v>
       </c>
       <c r="J62" s="20" t="s">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="K62" s="20" t="s">
-        <v>264</v>
+        <v>434</v>
       </c>
       <c r="L62" s="22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M62" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N62" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M62,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O62" s="24" t="n">
         <f aca="false">L62*(1+N62)</f>
-        <v>1.8</v>
+        <v>0.675</v>
       </c>
       <c r="P62" s="25" t="n">
         <f aca="false">O62*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q62" s="26"/>
       <c r="R62" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S62" s="20" t="s">
-        <v>336</v>
+        <v>435</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8007,32 +8136,32 @@
       <c r="B63" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="21" t="s">
-        <v>51</v>
+      <c r="C63" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G63" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K63" s="20" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="L63" s="22" t="n">
         <v>3</v>
@@ -8057,7 +8186,7 @@
         <v>106</v>
       </c>
       <c r="S63" s="20" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8068,56 +8197,56 @@
         <v>10</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="G64" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J64" s="20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K64" s="20" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="L64" s="22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M64" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N64" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M64,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O64" s="24" t="n">
         <f aca="false">L64*(1+N64)</f>
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="P64" s="25" t="n">
         <f aca="false">O64*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q64" s="26"/>
       <c r="R64" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S64" s="20" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8128,56 +8257,56 @@
         <v>10</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J65" s="20" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="K65" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N65" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M65,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O65" s="24" t="n">
         <f aca="false">L65*(1+N65)</f>
-        <v>0.55</v>
+        <v>2.4</v>
       </c>
       <c r="P65" s="25" t="n">
         <f aca="false">O65*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q65" s="26"/>
       <c r="R65" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S65" s="20" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8187,57 +8316,57 @@
       <c r="B66" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="21" t="s">
-        <v>52</v>
+      <c r="C66" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>297</v>
+        <v>388</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J66" s="20" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="K66" s="20" t="s">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="L66" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N66" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M66,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O66" s="24" t="n">
         <f aca="false">L66*(1+N66)</f>
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="P66" s="25" t="n">
         <f aca="false">O66*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q66" s="26"/>
       <c r="R66" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S66" s="20" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8248,56 +8377,56 @@
         <v>10</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="I67" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="K67" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N67" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M67,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O67" s="24" t="n">
         <f aca="false">L67*(1+N67)</f>
-        <v>1.8</v>
+        <v>0.55</v>
       </c>
       <c r="P67" s="25" t="n">
         <f aca="false">O67*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q67" s="26"/>
       <c r="R67" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S67" s="20" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8308,56 +8437,56 @@
         <v>10</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>452</v>
+        <v>19</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>246</v>
+        <v>437</v>
       </c>
       <c r="I68" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J68" s="20" t="s">
-        <v>455</v>
+        <v>104</v>
       </c>
       <c r="K68" s="20" t="s">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="L68" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M68" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N68" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M68,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O68" s="24" t="n">
         <f aca="false">L68*(1+N68)</f>
-        <v>0.55</v>
+        <v>1.8</v>
       </c>
       <c r="P68" s="25" t="n">
         <f aca="false">O68*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="Q68" s="26"/>
       <c r="R68" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S68" s="20" t="s">
-        <v>456</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8367,57 +8496,57 @@
       <c r="B69" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C69" s="20" t="s">
-        <v>52</v>
+      <c r="C69" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>189</v>
+        <v>388</v>
       </c>
       <c r="I69" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J69" s="20" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="K69" s="20" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L69" s="22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M69" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N69" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M69,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="O69" s="24" t="n">
         <f aca="false">L69*(1+N69)</f>
-        <v>1.65</v>
+        <v>4.05</v>
       </c>
       <c r="P69" s="25" t="n">
         <f aca="false">O69*Assumptions!$B$3</f>
-        <v>6.6</v>
+        <v>16.2</v>
       </c>
       <c r="Q69" s="26"/>
       <c r="R69" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S69" s="20" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8428,34 +8557,34 @@
         <v>10</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="I70" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J70" s="20" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="K70" s="20" t="s">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M70" s="22" t="s">
         <v>86</v>
@@ -8466,18 +8595,18 @@
       </c>
       <c r="O70" s="24" t="n">
         <f aca="false">L70*(1+N70)</f>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="P70" s="25" t="n">
         <f aca="false">O70*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q70" s="26"/>
       <c r="R70" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S70" s="20" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8488,56 +8617,56 @@
         <v>10</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="I71" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="K71" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="M71" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N71" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M71,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O71" s="24" t="n">
         <f aca="false">L71*(1+N71)</f>
-        <v>3.6</v>
+        <v>0.55</v>
       </c>
       <c r="P71" s="25" t="n">
         <f aca="false">O71*Assumptions!$B$3</f>
-        <v>14.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q71" s="26"/>
       <c r="R71" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S71" s="20" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8547,35 +8676,35 @@
       <c r="B72" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="21" t="s">
         <v>52</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>458</v>
+        <v>323</v>
       </c>
       <c r="I72" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J72" s="20" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="K72" s="20" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="L72" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M72" s="22" t="s">
         <v>86</v>
@@ -8586,18 +8715,18 @@
       </c>
       <c r="O72" s="24" t="n">
         <f aca="false">L72*(1+N72)</f>
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P72" s="25" t="n">
         <f aca="false">O72*Assumptions!$B$3</f>
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Q72" s="26"/>
       <c r="R72" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S72" s="20" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8607,32 +8736,32 @@
       <c r="B73" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C73" s="21" t="s">
-        <v>53</v>
+      <c r="C73" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>212</v>
+        <v>480</v>
       </c>
       <c r="I73" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J73" s="20" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="K73" s="20" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="L73" s="22" t="n">
         <v>1.5</v>
@@ -8657,7 +8786,7 @@
         <v>106</v>
       </c>
       <c r="S73" s="20" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8668,56 +8797,56 @@
         <v>10</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="G74" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>358</v>
+        <v>492</v>
       </c>
       <c r="I74" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J74" s="20" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="K74" s="20" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="L74" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M74" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N74" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M74,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O74" s="24" t="n">
         <f aca="false">L74*(1+N74)</f>
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P74" s="25" t="n">
         <f aca="false">O74*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q74" s="26"/>
       <c r="R74" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S74" s="20" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8728,56 +8857,56 @@
         <v>10</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="G75" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>478</v>
+        <v>268</v>
       </c>
       <c r="I75" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="20" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="K75" s="20" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="L75" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M75" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N75" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M75,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O75" s="24" t="n">
         <f aca="false">L75*(1+N75)</f>
-        <v>1.2</v>
+        <v>0.55</v>
       </c>
       <c r="P75" s="25" t="n">
         <f aca="false">O75*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q75" s="26"/>
       <c r="R75" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S75" s="20" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8788,34 +8917,34 @@
         <v>10</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>478</v>
+        <v>191</v>
       </c>
       <c r="I76" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J76" s="20" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="K76" s="20" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="L76" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M76" s="22" t="s">
         <v>84</v>
@@ -8826,18 +8955,18 @@
       </c>
       <c r="O76" s="24" t="n">
         <f aca="false">L76*(1+N76)</f>
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="P76" s="25" t="n">
         <f aca="false">O76*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="Q76" s="26"/>
       <c r="R76" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S76" s="20" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8848,56 +8977,56 @@
         <v>10</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>489</v>
+        <v>410</v>
       </c>
       <c r="I77" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J77" s="20" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="K77" s="20" t="s">
-        <v>198</v>
+        <v>347</v>
       </c>
       <c r="L77" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M77" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N77" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M77,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O77" s="24" t="n">
         <f aca="false">L77*(1+N77)</f>
-        <v>0.55</v>
+        <v>1.2</v>
       </c>
       <c r="P77" s="25" t="n">
         <f aca="false">O77*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q77" s="26"/>
       <c r="R77" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S77" s="20" t="s">
-        <v>104</v>
+        <v>510</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8907,35 +9036,35 @@
       <c r="B78" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="21" t="s">
-        <v>54</v>
+      <c r="C78" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>358</v>
+        <v>480</v>
       </c>
       <c r="I78" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J78" s="20" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="K78" s="20" t="s">
-        <v>507</v>
+        <v>200</v>
       </c>
       <c r="L78" s="22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M78" s="22" t="s">
         <v>86</v>
@@ -8946,18 +9075,18 @@
       </c>
       <c r="O78" s="24" t="n">
         <f aca="false">L78*(1+N78)</f>
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="P78" s="25" t="n">
         <f aca="false">O78*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="Q78" s="26"/>
       <c r="R78" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S78" s="20" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8968,34 +9097,34 @@
         <v>10</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>128</v>
+        <v>501</v>
       </c>
       <c r="I79" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J79" s="20" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="K79" s="20" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="L79" s="22" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M79" s="22" t="s">
         <v>86</v>
@@ -9006,18 +9135,18 @@
       </c>
       <c r="O79" s="24" t="n">
         <f aca="false">L79*(1+N79)</f>
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="P79" s="25" t="n">
         <f aca="false">O79*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="Q79" s="26"/>
       <c r="R79" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S79" s="20" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9027,35 +9156,35 @@
       <c r="B80" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C80" s="20" t="s">
-        <v>54</v>
+      <c r="C80" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="D80" s="20" t="s">
-        <v>19</v>
+        <v>520</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>469</v>
+        <v>234</v>
       </c>
       <c r="I80" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J80" s="20" t="s">
-        <v>104</v>
+        <v>523</v>
       </c>
       <c r="K80" s="20" t="s">
-        <v>264</v>
+        <v>524</v>
       </c>
       <c r="L80" s="22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M80" s="22" t="s">
         <v>86</v>
@@ -9066,18 +9195,18 @@
       </c>
       <c r="O80" s="24" t="n">
         <f aca="false">L80*(1+N80)</f>
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="P80" s="25" t="n">
         <f aca="false">O80*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q80" s="26"/>
       <c r="R80" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S80" s="20" t="s">
-        <v>336</v>
+        <v>525</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9088,56 +9217,56 @@
         <v>10</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>520</v>
+        <v>388</v>
       </c>
       <c r="I81" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>104</v>
+        <v>529</v>
       </c>
       <c r="K81" s="20" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M81" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N81" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M81,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O81" s="24" t="n">
         <f aca="false">L81*(1+N81)</f>
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="P81" s="25" t="n">
         <f aca="false">O81*Assumptions!$B$3</f>
-        <v>10.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q81" s="26"/>
       <c r="R81" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S81" s="20" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9148,34 +9277,34 @@
         <v>10</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I82" s="20" t="s">
         <v>31</v>
       </c>
       <c r="J82" s="20" t="s">
-        <v>104</v>
+        <v>534</v>
       </c>
       <c r="K82" s="20" t="s">
-        <v>340</v>
+        <v>237</v>
       </c>
       <c r="L82" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M82" s="22" t="s">
         <v>86</v>
@@ -9186,18 +9315,18 @@
       </c>
       <c r="O82" s="24" t="n">
         <f aca="false">L82*(1+N82)</f>
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="P82" s="25" t="n">
         <f aca="false">O82*Assumptions!$B$3</f>
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q82" s="26"/>
       <c r="R82" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S82" s="20" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9207,57 +9336,57 @@
       <c r="B83" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C83" s="21" t="s">
-        <v>55</v>
+      <c r="C83" s="20" t="s">
+        <v>53</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>246</v>
+        <v>521</v>
       </c>
       <c r="I83" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J83" s="20" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="K83" s="20" t="s">
-        <v>215</v>
+        <v>540</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M83" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N83" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M83,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O83" s="24" t="n">
         <f aca="false">L83*(1+N83)</f>
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="P83" s="25" t="n">
         <f aca="false">O83*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q83" s="26"/>
       <c r="R83" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S83" s="20" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9268,56 +9397,56 @@
         <v>10</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D84" s="20" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="E84" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="F84" s="20" t="s">
-        <v>533</v>
-      </c>
-      <c r="G84" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H84" s="20" t="s">
-        <v>358</v>
-      </c>
       <c r="I84" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J84" s="20" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="K84" s="20" t="s">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M84" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N84" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M84,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O84" s="24" t="n">
         <f aca="false">L84*(1+N84)</f>
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="P84" s="25" t="n">
         <f aca="false">O84*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q84" s="26"/>
       <c r="R84" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S84" s="20" t="s">
-        <v>535</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9327,35 +9456,35 @@
       <c r="B85" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="20" t="s">
-        <v>55</v>
+      <c r="C85" s="21" t="s">
+        <v>54</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>527</v>
+        <v>388</v>
       </c>
       <c r="I85" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J85" s="20" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="K85" s="20" t="s">
-        <v>198</v>
+        <v>550</v>
       </c>
       <c r="L85" s="22" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M85" s="22" t="s">
         <v>86</v>
@@ -9366,18 +9495,18 @@
       </c>
       <c r="O85" s="24" t="n">
         <f aca="false">L85*(1+N85)</f>
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="P85" s="25" t="n">
         <f aca="false">O85*Assumptions!$B$3</f>
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="Q85" s="26"/>
       <c r="R85" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S85" s="20" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9388,56 +9517,56 @@
         <v>10</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D86" s="20" t="s">
-        <v>351</v>
+        <v>552</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>352</v>
+        <v>130</v>
       </c>
       <c r="I86" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J86" s="20" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="K86" s="20" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M86" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N86" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M86,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O86" s="24" t="n">
         <f aca="false">L86*(1+N86)</f>
-        <v>0.675</v>
+        <v>1.2</v>
       </c>
       <c r="P86" s="25" t="n">
         <f aca="false">O86*Assumptions!$B$3</f>
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q86" s="26"/>
       <c r="R86" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S86" s="20" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9447,57 +9576,57 @@
       <c r="B87" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C87" s="21" t="s">
-        <v>56</v>
+      <c r="C87" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>177</v>
+        <v>512</v>
       </c>
       <c r="I87" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J87" s="20" t="s">
-        <v>549</v>
+        <v>104</v>
       </c>
       <c r="K87" s="20" t="s">
-        <v>550</v>
+        <v>286</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M87" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N87" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M87,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O87" s="24" t="n">
         <f aca="false">L87*(1+N87)</f>
-        <v>3.375</v>
+        <v>2.4</v>
       </c>
       <c r="P87" s="25" t="n">
         <f aca="false">O87*Assumptions!$B$3</f>
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q87" s="26"/>
       <c r="R87" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S87" s="20" t="s">
-        <v>551</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9508,34 +9637,34 @@
         <v>10</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D88" s="20" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="I88" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J88" s="20" t="s">
-        <v>555</v>
+        <v>104</v>
       </c>
       <c r="K88" s="20" t="s">
-        <v>556</v>
+        <v>157</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M88" s="22" t="s">
         <v>88</v>
@@ -9546,18 +9675,18 @@
       </c>
       <c r="O88" s="24" t="n">
         <f aca="false">L88*(1+N88)</f>
-        <v>3.375</v>
+        <v>2.7</v>
       </c>
       <c r="P88" s="25" t="n">
         <f aca="false">O88*Assumptions!$B$3</f>
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q88" s="26"/>
       <c r="R88" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S88" s="20" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9568,34 +9697,34 @@
         <v>10</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="I89" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="K89" s="20" t="s">
-        <v>562</v>
+        <v>370</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M89" s="22" t="s">
         <v>86</v>
@@ -9606,18 +9735,18 @@
       </c>
       <c r="O89" s="24" t="n">
         <f aca="false">L89*(1+N89)</f>
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="P89" s="25" t="n">
         <f aca="false">O89*Assumptions!$B$3</f>
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q89" s="26"/>
       <c r="R89" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S89" s="20" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9627,35 +9756,35 @@
       <c r="B90" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C90" s="20" t="s">
-        <v>56</v>
+      <c r="C90" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>567</v>
+        <v>268</v>
       </c>
       <c r="I90" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J90" s="20" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="K90" s="20" t="s">
-        <v>569</v>
+        <v>237</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90" s="22" t="s">
         <v>86</v>
@@ -9666,18 +9795,18 @@
       </c>
       <c r="O90" s="24" t="n">
         <f aca="false">L90*(1+N90)</f>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P90" s="25" t="n">
         <f aca="false">O90*Assumptions!$B$3</f>
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
       <c r="Q90" s="26"/>
       <c r="R90" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S90" s="20" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,35 +9816,35 @@
       <c r="B91" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="21" t="s">
-        <v>57</v>
+      <c r="C91" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>303</v>
+        <v>388</v>
       </c>
       <c r="I91" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="K91" s="20" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M91" s="22" t="s">
         <v>86</v>
@@ -9726,18 +9855,18 @@
       </c>
       <c r="O91" s="24" t="n">
         <f aca="false">L91*(1+N91)</f>
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="P91" s="25" t="n">
         <f aca="false">O91*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="Q91" s="26"/>
       <c r="R91" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S91" s="20" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9748,56 +9877,56 @@
         <v>10</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D92" s="20" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G92" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I92" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J92" s="20" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K92" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="M92" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N92" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M92,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O92" s="24" t="n">
         <f aca="false">L92*(1+N92)</f>
-        <v>0.55</v>
+        <v>3</v>
       </c>
       <c r="P92" s="25" t="n">
         <f aca="false">O92*Assumptions!$B$3</f>
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="Q92" s="26"/>
       <c r="R92" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S92" s="20" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9808,56 +9937,56 @@
         <v>10</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D93" s="20" t="s">
-        <v>580</v>
+        <v>381</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>443</v>
+        <v>382</v>
       </c>
       <c r="I93" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J93" s="20" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="K93" s="20" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M93" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N93" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M93,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O93" s="24" t="n">
         <f aca="false">L93*(1+N93)</f>
-        <v>2.4</v>
+        <v>0.675</v>
       </c>
       <c r="P93" s="25" t="n">
         <f aca="false">O93*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q93" s="26"/>
       <c r="R93" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S93" s="20" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9867,57 +9996,57 @@
       <c r="B94" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="20" t="s">
-        <v>57</v>
+      <c r="C94" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="D94" s="20" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G94" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="I94" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J94" s="20" t="s">
-        <v>154</v>
+        <v>592</v>
       </c>
       <c r="K94" s="20" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M94" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N94" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M94,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O94" s="24" t="n">
         <f aca="false">L94*(1+N94)</f>
-        <v>1.2</v>
+        <v>3.375</v>
       </c>
       <c r="P94" s="25" t="n">
         <f aca="false">O94*Assumptions!$B$3</f>
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="Q94" s="26"/>
       <c r="R94" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S94" s="20" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9928,56 +10057,56 @@
         <v>10</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="G95" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>523</v>
+        <v>590</v>
       </c>
       <c r="I95" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J95" s="20" t="s">
-        <v>104</v>
+        <v>598</v>
       </c>
       <c r="K95" s="20" t="s">
-        <v>104</v>
+        <v>599</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="M95" s="22" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N95" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M95,Assumptions!$A$13:$A$16,0))</f>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O95" s="24" t="n">
         <f aca="false">L95*(1+N95)</f>
-        <v>6</v>
+        <v>3.375</v>
       </c>
       <c r="P95" s="25" t="n">
         <f aca="false">O95*Assumptions!$B$3</f>
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="Q95" s="26"/>
       <c r="R95" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S95" s="20" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9988,56 +10117,56 @@
         <v>10</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D96" s="20" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="G96" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>104</v>
+        <v>590</v>
       </c>
       <c r="I96" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J96" s="20" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="K96" s="20" t="s">
-        <v>481</v>
+        <v>605</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M96" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N96" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M96,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="O96" s="24" t="n">
         <f aca="false">L96*(1+N96)</f>
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="P96" s="25" t="n">
         <f aca="false">O96*Assumptions!$B$3</f>
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="Q96" s="26"/>
       <c r="R96" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S96" s="20" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10048,34 +10177,34 @@
         <v>10</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>19</v>
+        <v>607</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>565</v>
+        <v>610</v>
       </c>
       <c r="I97" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J97" s="20" t="s">
-        <v>104</v>
+        <v>611</v>
       </c>
       <c r="K97" s="20" t="s">
-        <v>264</v>
+        <v>612</v>
       </c>
       <c r="L97" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M97" s="22" t="s">
         <v>86</v>
@@ -10086,18 +10215,18 @@
       </c>
       <c r="O97" s="24" t="n">
         <f aca="false">L97*(1+N97)</f>
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="P97" s="25" t="n">
         <f aca="false">O97*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="Q97" s="26"/>
       <c r="R97" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S97" s="20" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10107,35 +10236,35 @@
       <c r="B98" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C98" s="20" t="s">
+      <c r="C98" s="21" t="s">
         <v>57</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>553</v>
+        <v>329</v>
       </c>
       <c r="I98" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J98" s="20" t="s">
-        <v>104</v>
+        <v>617</v>
       </c>
       <c r="K98" s="20" t="s">
-        <v>340</v>
+        <v>122</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="22" t="s">
         <v>86</v>
@@ -10146,438 +10275,438 @@
       </c>
       <c r="O98" s="24" t="n">
         <f aca="false">L98*(1+N98)</f>
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="P98" s="25" t="n">
         <f aca="false">O98*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q98" s="26"/>
       <c r="R98" s="26" t="s">
         <v>106</v>
       </c>
       <c r="S98" s="20" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="27" t="n">
+      <c r="A99" s="20" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>607</v>
-      </c>
-      <c r="D99" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>609</v>
-      </c>
-      <c r="F99" s="27" t="s">
-        <v>610</v>
-      </c>
-      <c r="G99" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H99" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I99" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J99" s="27" t="s">
-        <v>613</v>
-      </c>
-      <c r="K99" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L99" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="M99" s="29" t="s">
+      <c r="B99" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="G99" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="I99" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J99" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="K99" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M99" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="N99" s="23" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M99,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.1</v>
+      </c>
+      <c r="O99" s="24" t="n">
+        <f aca="false">L99*(1+N99)</f>
+        <v>0.55</v>
+      </c>
+      <c r="P99" s="25" t="n">
+        <f aca="false">O99*Assumptions!$B$3</f>
+        <v>2.2</v>
+      </c>
+      <c r="Q99" s="26"/>
+      <c r="R99" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="S99" s="20" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="20" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>480</v>
+      </c>
+      <c r="I100" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J100" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="K100" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M100" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="N99" s="30" t="n">
-        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M99,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
-      </c>
-      <c r="O99" s="31" t="n">
-        <f aca="false">L99*(1+N99)</f>
-        <v>7.2</v>
-      </c>
-      <c r="P99" s="32" t="n">
-        <f aca="false">O99*Assumptions!$B$3</f>
-        <v>28.8</v>
-      </c>
-      <c r="Q99" s="27"/>
-      <c r="R99" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="S99" s="27" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="27" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C100" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D100" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E100" s="27" t="s">
-        <v>616</v>
-      </c>
-      <c r="F100" s="27" t="s">
-        <v>617</v>
-      </c>
-      <c r="G100" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H100" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I100" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J100" s="27" t="s">
-        <v>618</v>
-      </c>
-      <c r="K100" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L100" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="M100" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="N100" s="30" t="n">
+      <c r="N100" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M100,Assumptions!$A$13:$A$16,0))</f>
         <v>0.2</v>
       </c>
-      <c r="O100" s="31" t="n">
+      <c r="O100" s="24" t="n">
         <f aca="false">L100*(1+N100)</f>
-        <v>7.2</v>
-      </c>
-      <c r="P100" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P100" s="25" t="n">
         <f aca="false">O100*Assumptions!$B$3</f>
-        <v>28.8</v>
-      </c>
-      <c r="Q100" s="27"/>
-      <c r="R100" s="27" t="s">
+        <v>9.6</v>
+      </c>
+      <c r="Q100" s="26"/>
+      <c r="R100" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="S100" s="27" t="s">
-        <v>615</v>
+      <c r="S100" s="20" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="27" t="n">
+      <c r="A101" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D101" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>619</v>
-      </c>
-      <c r="F101" s="27" t="s">
-        <v>620</v>
-      </c>
-      <c r="G101" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H101" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I101" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J101" s="27" t="s">
-        <v>621</v>
-      </c>
-      <c r="K101" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L101" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="M101" s="29" t="s">
+      <c r="B101" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="G101" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I101" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J101" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="K101" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="N101" s="30" t="n">
+      <c r="N101" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M101,Assumptions!$A$13:$A$16,0))</f>
         <v>0.2</v>
       </c>
-      <c r="O101" s="31" t="n">
+      <c r="O101" s="24" t="n">
         <f aca="false">L101*(1+N101)</f>
+        <v>1.2</v>
+      </c>
+      <c r="P101" s="25" t="n">
+        <f aca="false">O101*Assumptions!$B$3</f>
         <v>4.8</v>
       </c>
-      <c r="P101" s="32" t="n">
-        <f aca="false">O101*Assumptions!$B$3</f>
-        <v>19.2</v>
-      </c>
-      <c r="Q101" s="27"/>
-      <c r="R101" s="27" t="s">
+      <c r="Q101" s="26"/>
+      <c r="R101" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="S101" s="27" t="s">
-        <v>615</v>
+      <c r="S101" s="20" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="27" t="n">
+      <c r="A102" s="20" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C102" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D102" s="27" t="s">
+      <c r="B102" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="I102" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J102" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K102" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M102" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N102" s="23" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M102,Assumptions!$A$13:$A$16,0))</f>
+        <v>0</v>
+      </c>
+      <c r="O102" s="24" t="n">
+        <f aca="false">L102*(1+N102)</f>
+        <v>6</v>
+      </c>
+      <c r="P102" s="25" t="n">
+        <f aca="false">O102*Assumptions!$B$3</f>
+        <v>24</v>
+      </c>
+      <c r="Q102" s="26"/>
+      <c r="R102" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="S102" s="20" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="F103" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="G103" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I103" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J103" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="K103" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="N103" s="23" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M103,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.35</v>
+      </c>
+      <c r="O103" s="24" t="n">
+        <f aca="false">L103*(1+N103)</f>
+        <v>1.35</v>
+      </c>
+      <c r="P103" s="25" t="n">
+        <f aca="false">O103*Assumptions!$B$3</f>
+        <v>5.4</v>
+      </c>
+      <c r="Q103" s="26"/>
+      <c r="R103" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="S103" s="20" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="20" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="G104" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="20" t="s">
         <v>608</v>
       </c>
-      <c r="E102" s="27" t="s">
-        <v>622</v>
-      </c>
-      <c r="F102" s="27" t="s">
-        <v>623</v>
-      </c>
-      <c r="G102" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H102" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I102" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J102" s="27" t="s">
-        <v>624</v>
-      </c>
-      <c r="K102" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L102" s="29" t="n">
+      <c r="I104" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J104" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K104" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="L104" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="M102" s="29" t="s">
+      <c r="M104" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="N102" s="30" t="n">
-        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M102,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
-      </c>
-      <c r="O102" s="31" t="n">
-        <f aca="false">L102*(1+N102)</f>
-        <v>2.4</v>
-      </c>
-      <c r="P102" s="32" t="n">
-        <f aca="false">O102*Assumptions!$B$3</f>
-        <v>9.6</v>
-      </c>
-      <c r="Q102" s="27"/>
-      <c r="R102" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="S102" s="27" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="27" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C103" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D103" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>625</v>
-      </c>
-      <c r="F103" s="27" t="s">
-        <v>626</v>
-      </c>
-      <c r="G103" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H103" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I103" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J103" s="27" t="s">
-        <v>627</v>
-      </c>
-      <c r="K103" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L103" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M103" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="N103" s="30" t="n">
-        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M103,Assumptions!$A$13:$A$16,0))</f>
-        <v>0.2</v>
-      </c>
-      <c r="O103" s="31" t="n">
-        <f aca="false">L103*(1+N103)</f>
-        <v>6</v>
-      </c>
-      <c r="P103" s="32" t="n">
-        <f aca="false">O103*Assumptions!$B$3</f>
-        <v>24</v>
-      </c>
-      <c r="Q103" s="27"/>
-      <c r="R103" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="S103" s="27" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="27" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D104" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>628</v>
-      </c>
-      <c r="F104" s="27" t="s">
-        <v>629</v>
-      </c>
-      <c r="G104" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H104" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I104" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J104" s="27" t="s">
-        <v>630</v>
-      </c>
-      <c r="K104" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L104" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M104" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="N104" s="30" t="n">
+      <c r="N104" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M104,Assumptions!$A$13:$A$16,0))</f>
         <v>0.2</v>
       </c>
-      <c r="O104" s="31" t="n">
+      <c r="O104" s="24" t="n">
         <f aca="false">L104*(1+N104)</f>
-        <v>3.6</v>
-      </c>
-      <c r="P104" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P104" s="25" t="n">
         <f aca="false">O104*Assumptions!$B$3</f>
-        <v>14.4</v>
-      </c>
-      <c r="Q104" s="27"/>
-      <c r="R104" s="27" t="s">
+        <v>9.6</v>
+      </c>
+      <c r="Q104" s="26"/>
+      <c r="R104" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="S104" s="27" t="s">
-        <v>615</v>
+      <c r="S104" s="20" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="27" t="n">
+      <c r="A105" s="20" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C105" s="27" t="s">
-        <v>607</v>
-      </c>
-      <c r="D105" s="27" t="s">
-        <v>608</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>631</v>
-      </c>
-      <c r="F105" s="27" t="s">
-        <v>632</v>
-      </c>
-      <c r="G105" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H105" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I105" s="27" t="s">
-        <v>612</v>
-      </c>
-      <c r="J105" s="27" t="s">
-        <v>598</v>
-      </c>
-      <c r="K105" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="L105" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M105" s="29" t="s">
+      <c r="B105" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="I105" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J105" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K105" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M105" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="N105" s="30" t="n">
+      <c r="N105" s="23" t="n">
         <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M105,Assumptions!$A$13:$A$16,0))</f>
         <v>0.2</v>
       </c>
-      <c r="O105" s="31" t="n">
+      <c r="O105" s="24" t="n">
         <f aca="false">L105*(1+N105)</f>
-        <v>7.8</v>
-      </c>
-      <c r="P105" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P105" s="25" t="n">
         <f aca="false">O105*Assumptions!$B$3</f>
-        <v>31.2</v>
-      </c>
-      <c r="Q105" s="27"/>
-      <c r="R105" s="27" t="s">
+        <v>9.6</v>
+      </c>
+      <c r="Q105" s="26"/>
+      <c r="R105" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="S105" s="27" t="s">
-        <v>615</v>
+      <c r="S105" s="20" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10587,35 +10716,35 @@
       <c r="B106" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C106" s="27" t="s">
-        <v>607</v>
+      <c r="C106" s="28" t="s">
+        <v>650</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E106" s="27" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="F106" s="27" t="s">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="G106" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H106" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I106" s="27" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="J106" s="27" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="K106" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L106" s="29" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="M106" s="29" t="s">
         <v>86</v>
@@ -10626,18 +10755,18 @@
       </c>
       <c r="O106" s="31" t="n">
         <f aca="false">L106*(1+N106)</f>
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="P106" s="32" t="n">
         <f aca="false">O106*Assumptions!$B$3</f>
-        <v>12</v>
+        <v>28.8</v>
       </c>
       <c r="Q106" s="27"/>
       <c r="R106" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S106" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10648,34 +10777,34 @@
         <v>11</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="F107" s="27" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="G107" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H107" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I107" s="27" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="J107" s="27" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="K107" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L107" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M107" s="29" t="s">
         <v>86</v>
@@ -10686,18 +10815,18 @@
       </c>
       <c r="O107" s="31" t="n">
         <f aca="false">L107*(1+N107)</f>
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="P107" s="32" t="n">
         <f aca="false">O107*Assumptions!$B$3</f>
-        <v>14.4</v>
+        <v>28.8</v>
       </c>
       <c r="Q107" s="27"/>
       <c r="R107" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S107" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10708,34 +10837,34 @@
         <v>11</v>
       </c>
       <c r="C108" s="27" t="s">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E108" s="27" t="s">
-        <v>639</v>
+        <v>662</v>
       </c>
       <c r="F108" s="27" t="s">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="G108" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H108" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I108" s="27" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="J108" s="27" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
       <c r="K108" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L108" s="29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M108" s="29" t="s">
         <v>86</v>
@@ -10746,18 +10875,18 @@
       </c>
       <c r="O108" s="31" t="n">
         <f aca="false">L108*(1+N108)</f>
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="P108" s="32" t="n">
         <f aca="false">O108*Assumptions!$B$3</f>
-        <v>9.6</v>
+        <v>19.2</v>
       </c>
       <c r="Q108" s="27"/>
       <c r="R108" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S108" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10767,35 +10896,35 @@
       <c r="B109" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="28" t="s">
-        <v>642</v>
+      <c r="C109" s="27" t="s">
+        <v>650</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="F109" s="27" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="G109" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H109" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I109" s="27" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="J109" s="27" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="K109" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L109" s="29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M109" s="29" t="s">
         <v>86</v>
@@ -10806,18 +10935,18 @@
       </c>
       <c r="O109" s="31" t="n">
         <f aca="false">L109*(1+N109)</f>
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="P109" s="32" t="n">
         <f aca="false">O109*Assumptions!$B$3</f>
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="Q109" s="27"/>
       <c r="R109" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S109" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10828,34 +10957,34 @@
         <v>11</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="F110" s="27" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="G110" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H110" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I110" s="27" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="J110" s="27" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="K110" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L110" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M110" s="29" t="s">
         <v>86</v>
@@ -10866,18 +10995,18 @@
       </c>
       <c r="O110" s="31" t="n">
         <f aca="false">L110*(1+N110)</f>
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="P110" s="32" t="n">
         <f aca="false">O110*Assumptions!$B$3</f>
-        <v>19.2</v>
+        <v>24</v>
       </c>
       <c r="Q110" s="27"/>
       <c r="R110" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S110" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10888,34 +11017,34 @@
         <v>11</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E111" s="27" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="F111" s="27" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="G111" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H111" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I111" s="27" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="J111" s="27" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="K111" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L111" s="29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M111" s="29" t="s">
         <v>86</v>
@@ -10926,18 +11055,18 @@
       </c>
       <c r="O111" s="31" t="n">
         <f aca="false">L111*(1+N111)</f>
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="P111" s="32" t="n">
         <f aca="false">O111*Assumptions!$B$3</f>
-        <v>48</v>
+        <v>14.4</v>
       </c>
       <c r="Q111" s="27"/>
       <c r="R111" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S111" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10948,34 +11077,34 @@
         <v>11</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="F112" s="27" t="s">
+        <v>675</v>
+      </c>
+      <c r="G112" s="27" t="s">
         <v>654</v>
       </c>
-      <c r="G112" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="H112" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I112" s="27" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="J112" s="27" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="K112" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L112" s="29" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="M112" s="29" t="s">
         <v>86</v>
@@ -10986,18 +11115,18 @@
       </c>
       <c r="O112" s="31" t="n">
         <f aca="false">L112*(1+N112)</f>
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="P112" s="32" t="n">
         <f aca="false">O112*Assumptions!$B$3</f>
-        <v>14.4</v>
+        <v>31.2</v>
       </c>
       <c r="Q112" s="27"/>
       <c r="R112" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S112" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11008,34 +11137,34 @@
         <v>11</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="F113" s="27" t="s">
+        <v>677</v>
+      </c>
+      <c r="G113" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H113" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I113" s="27" t="s">
+        <v>655</v>
+      </c>
+      <c r="J113" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="K113" s="27" t="s">
         <v>657</v>
       </c>
-      <c r="G113" s="27" t="s">
-        <v>611</v>
-      </c>
-      <c r="H113" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I113" s="27" t="s">
-        <v>645</v>
-      </c>
-      <c r="J113" s="27" t="s">
-        <v>658</v>
-      </c>
-      <c r="K113" s="27" t="s">
-        <v>614</v>
-      </c>
       <c r="L113" s="29" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="M113" s="29" t="s">
         <v>86</v>
@@ -11046,18 +11175,18 @@
       </c>
       <c r="O113" s="31" t="n">
         <f aca="false">L113*(1+N113)</f>
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="P113" s="32" t="n">
         <f aca="false">O113*Assumptions!$B$3</f>
-        <v>28.8</v>
+        <v>12</v>
       </c>
       <c r="Q113" s="27"/>
       <c r="R113" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S113" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11067,35 +11196,35 @@
       <c r="B114" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C114" s="28" t="s">
-        <v>659</v>
+      <c r="C114" s="27" t="s">
+        <v>650</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E114" s="27" t="s">
-        <v>660</v>
+        <v>679</v>
       </c>
       <c r="F114" s="27" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="G114" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H114" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I114" s="27" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="J114" s="27" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="K114" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L114" s="29" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M114" s="29" t="s">
         <v>86</v>
@@ -11106,18 +11235,18 @@
       </c>
       <c r="O114" s="31" t="n">
         <f aca="false">L114*(1+N114)</f>
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="P114" s="32" t="n">
         <f aca="false">O114*Assumptions!$B$3</f>
-        <v>96</v>
+        <v>14.4</v>
       </c>
       <c r="Q114" s="27"/>
       <c r="R114" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S114" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11128,34 +11257,34 @@
         <v>11</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>608</v>
+        <v>651</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="G115" s="27" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="H115" s="27" t="s">
         <v>10</v>
       </c>
       <c r="I115" s="27" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="J115" s="27" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="K115" s="27" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="L115" s="29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M115" s="29" t="s">
         <v>86</v>
@@ -11166,32 +11295,452 @@
       </c>
       <c r="O115" s="31" t="n">
         <f aca="false">L115*(1+N115)</f>
-        <v>9.6</v>
+        <v>2.4</v>
       </c>
       <c r="P115" s="32" t="n">
         <f aca="false">O115*Assumptions!$B$3</f>
-        <v>38.4</v>
+        <v>9.6</v>
       </c>
       <c r="Q115" s="27"/>
       <c r="R115" s="27" t="s">
         <v>106</v>
       </c>
       <c r="S115" s="27" t="s">
-        <v>615</v>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="27" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>686</v>
+      </c>
+      <c r="F116" s="27" t="s">
+        <v>687</v>
+      </c>
+      <c r="G116" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H116" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I116" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="J116" s="27" t="s">
+        <v>689</v>
+      </c>
+      <c r="K116" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L116" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N116" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M116,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O116" s="31" t="n">
+        <f aca="false">L116*(1+N116)</f>
+        <v>6</v>
+      </c>
+      <c r="P116" s="32" t="n">
+        <f aca="false">O116*Assumptions!$B$3</f>
+        <v>24</v>
+      </c>
+      <c r="Q116" s="27"/>
+      <c r="R116" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S116" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="D117" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>690</v>
+      </c>
+      <c r="F117" s="27" t="s">
+        <v>691</v>
+      </c>
+      <c r="G117" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H117" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I117" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="J117" s="27" t="s">
+        <v>692</v>
+      </c>
+      <c r="K117" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L117" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M117" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N117" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M117,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O117" s="31" t="n">
+        <f aca="false">L117*(1+N117)</f>
+        <v>4.8</v>
+      </c>
+      <c r="P117" s="32" t="n">
+        <f aca="false">O117*Assumptions!$B$3</f>
+        <v>19.2</v>
+      </c>
+      <c r="Q117" s="27"/>
+      <c r="R117" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S117" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="27" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>693</v>
+      </c>
+      <c r="F118" s="27" t="s">
+        <v>694</v>
+      </c>
+      <c r="G118" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H118" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I118" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="J118" s="27" t="s">
+        <v>695</v>
+      </c>
+      <c r="K118" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L118" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N118" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M118,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O118" s="31" t="n">
+        <f aca="false">L118*(1+N118)</f>
+        <v>12</v>
+      </c>
+      <c r="P118" s="32" t="n">
+        <f aca="false">O118*Assumptions!$B$3</f>
+        <v>48</v>
+      </c>
+      <c r="Q118" s="27"/>
+      <c r="R118" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S118" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="27" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E119" s="27" t="s">
+        <v>696</v>
+      </c>
+      <c r="F119" s="27" t="s">
+        <v>697</v>
+      </c>
+      <c r="G119" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H119" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I119" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="J119" s="27" t="s">
+        <v>698</v>
+      </c>
+      <c r="K119" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L119" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N119" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M119,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O119" s="31" t="n">
+        <f aca="false">L119*(1+N119)</f>
+        <v>3.6</v>
+      </c>
+      <c r="P119" s="32" t="n">
+        <f aca="false">O119*Assumptions!$B$3</f>
+        <v>14.4</v>
+      </c>
+      <c r="Q119" s="27"/>
+      <c r="R119" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S119" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="27" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="D120" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>699</v>
+      </c>
+      <c r="F120" s="27" t="s">
+        <v>700</v>
+      </c>
+      <c r="G120" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H120" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I120" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="J120" s="27" t="s">
+        <v>701</v>
+      </c>
+      <c r="K120" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L120" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M120" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N120" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M120,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O120" s="31" t="n">
+        <f aca="false">L120*(1+N120)</f>
+        <v>7.2</v>
+      </c>
+      <c r="P120" s="32" t="n">
+        <f aca="false">O120*Assumptions!$B$3</f>
+        <v>28.8</v>
+      </c>
+      <c r="Q120" s="27"/>
+      <c r="R120" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S120" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="28" t="s">
+        <v>702</v>
+      </c>
+      <c r="D121" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>703</v>
+      </c>
+      <c r="F121" s="27" t="s">
+        <v>704</v>
+      </c>
+      <c r="G121" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H121" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I121" s="27" t="s">
+        <v>705</v>
+      </c>
+      <c r="J121" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="K121" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L121" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="M121" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N121" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M121,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O121" s="31" t="n">
+        <f aca="false">L121*(1+N121)</f>
+        <v>24</v>
+      </c>
+      <c r="P121" s="32" t="n">
+        <f aca="false">O121*Assumptions!$B$3</f>
+        <v>96</v>
+      </c>
+      <c r="Q121" s="27"/>
+      <c r="R121" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S121" s="27" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>702</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>707</v>
+      </c>
+      <c r="F122" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="G122" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="H122" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I122" s="27" t="s">
+        <v>705</v>
+      </c>
+      <c r="J122" s="27" t="s">
+        <v>709</v>
+      </c>
+      <c r="K122" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="L122" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N122" s="30" t="n">
+        <f aca="false">INDEX(Assumptions!$B$13:$B$16,MATCH(M122,Assumptions!$A$13:$A$16,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="O122" s="31" t="n">
+        <f aca="false">L122*(1+N122)</f>
+        <v>9.6</v>
+      </c>
+      <c r="P122" s="32" t="n">
+        <f aca="false">O122*Assumptions!$B$3</f>
+        <v>38.4</v>
+      </c>
+      <c r="Q122" s="27"/>
+      <c r="R122" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="S122" s="27" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S115"/>
+  <autoFilter ref="A1:S122"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R115" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R122" type="list">
       <formula1>"Not started,In progress,In review,Done,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M115" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M122" type="list">
       <formula1>"N,L,M,H"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G115" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G122" type="list">
       <formula1>"BE,FE,QA,PM,BE/FE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11221,7 +11770,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>667</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11229,32 +11778,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>668</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>669</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>670</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>671</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>672</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>673</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11262,12 +11811,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>674</v>
+        <v>717</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>675</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
